--- a/artfynd/A 46144-2024 artfynd.xlsx
+++ b/artfynd/A 46144-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3981,7 +3981,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120285905</v>
+        <v>120285903</v>
       </c>
       <c r="B31" t="n">
         <v>90545</v>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768617</v>
+        <v>768552</v>
       </c>
       <c r="R31" t="n">
-        <v>7084860</v>
+        <v>7084960</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120285901</v>
+        <v>120285906</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
+        <v>90527</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768524</v>
+        <v>768617</v>
       </c>
       <c r="R32" t="n">
-        <v>7085136</v>
+        <v>7084860</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120285906</v>
+        <v>120285905</v>
       </c>
       <c r="B33" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4197,25 +4197,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120285903</v>
+        <v>120285901</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4401,25 +4401,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768552</v>
+        <v>768524</v>
       </c>
       <c r="R35" t="n">
-        <v>7084960</v>
+        <v>7085136</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,6 +4488,219 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120469533</v>
+      </c>
+      <c r="B36" t="n">
+        <v>94334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>degersjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>768525</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7085190</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Manne Frih</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Manne Frih</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120469518</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>degersjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>768525</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7085170</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Manne Frih</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Manne Frih</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46144-2024 artfynd.xlsx
+++ b/artfynd/A 46144-2024 artfynd.xlsx
@@ -3981,10 +3981,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120285903</v>
+        <v>120285904</v>
       </c>
       <c r="B31" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3993,25 +3993,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768552</v>
+        <v>768612</v>
       </c>
       <c r="R31" t="n">
-        <v>7084960</v>
+        <v>7084906</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120285906</v>
+        <v>120285901</v>
       </c>
       <c r="B32" t="n">
-        <v>90527</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768617</v>
+        <v>768524</v>
       </c>
       <c r="R32" t="n">
-        <v>7084860</v>
+        <v>7085136</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120285904</v>
+        <v>120285903</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4299,25 +4299,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768612</v>
+        <v>768552</v>
       </c>
       <c r="R34" t="n">
-        <v>7084906</v>
+        <v>7084960</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120285901</v>
+        <v>120285906</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>90527</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4405,21 +4405,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768524</v>
+        <v>768617</v>
       </c>
       <c r="R35" t="n">
-        <v>7085136</v>
+        <v>7084860</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 46144-2024 artfynd.xlsx
+++ b/artfynd/A 46144-2024 artfynd.xlsx
@@ -4083,10 +4083,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120285901</v>
+        <v>120285903</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4095,25 +4095,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768524</v>
+        <v>768552</v>
       </c>
       <c r="R32" t="n">
-        <v>7085136</v>
+        <v>7084960</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120285905</v>
+        <v>120285901</v>
       </c>
       <c r="B33" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4197,25 +4197,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>768617</v>
+        <v>768524</v>
       </c>
       <c r="R33" t="n">
-        <v>7084860</v>
+        <v>7085136</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120285903</v>
+        <v>120285906</v>
       </c>
       <c r="B34" t="n">
-        <v>90545</v>
+        <v>90527</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4299,25 +4299,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768552</v>
+        <v>768617</v>
       </c>
       <c r="R34" t="n">
-        <v>7084960</v>
+        <v>7084860</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120285906</v>
+        <v>120285905</v>
       </c>
       <c r="B35" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4401,25 +4401,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120469533</v>
+        <v>120469518</v>
       </c>
       <c r="B36" t="n">
-        <v>94334</v>
+        <v>79623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4503,31 +4503,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4538,7 +4537,7 @@
         <v>768525</v>
       </c>
       <c r="R36" t="n">
-        <v>7085190</v>
+        <v>7085170</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4598,10 +4597,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120469518</v>
+        <v>120469533</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>94334</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4610,30 +4609,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>768525</v>
       </c>
       <c r="R37" t="n">
-        <v>7085170</v>
+        <v>7085190</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>

--- a/artfynd/A 46144-2024 artfynd.xlsx
+++ b/artfynd/A 46144-2024 artfynd.xlsx
@@ -3981,10 +3981,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120285904</v>
+        <v>120285901</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768612</v>
+        <v>768524</v>
       </c>
       <c r="R31" t="n">
-        <v>7084906</v>
+        <v>7085136</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120285901</v>
+        <v>120285905</v>
       </c>
       <c r="B33" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4197,25 +4197,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>768524</v>
+        <v>768617</v>
       </c>
       <c r="R33" t="n">
-        <v>7085136</v>
+        <v>7084860</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120285906</v>
+        <v>120285904</v>
       </c>
       <c r="B34" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4303,21 +4303,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768617</v>
+        <v>768612</v>
       </c>
       <c r="R34" t="n">
-        <v>7084860</v>
+        <v>7084906</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120285905</v>
+        <v>120285906</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>90527</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4401,25 +4401,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
